--- a/示例数据/附件4：问题汇总.xlsx
+++ b/示例数据/附件4：问题汇总.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="145">
   <si>
     <t>编号</t>
   </si>
@@ -47,7 +47,7 @@
     <t>数据基本查询</t>
   </si>
   <si>
-    <t>[{"Q": "金花股份利润总额是多少"}, {"Q": "2025年第三季度的"}]</t>
+    <t>[{"Q":"金花股份利润总额是多少"},{"Q":"2025年第三季度的"}]</t>
   </si>
   <si>
     <t>B1002</t>
@@ -56,7 +56,415 @@
     <t>数据统计分析查询</t>
   </si>
   <si>
-    <t>[{"Q": "金花股份近几年的利润总额变化趋势是什么样的"}]</t>
+    <t>[{"Q":"金花股份近几年的利润总额变化趋势是什么样的"}]</t>
+  </si>
+  <si>
+    <t>B1003</t>
+  </si>
+  <si>
+    <t>[{"Q":"999与白云山相比，去年收益率最高的是"}]</t>
+  </si>
+  <si>
+    <t>B1004</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年前三季度，公司实现收入超过200亿元的企业有哪些"}]</t>
+  </si>
+  <si>
+    <t>B1005</t>
+  </si>
+  <si>
+    <t>[{"Q":"企业名称：三金，第三季度公司主营业务收入是多少"},{"Q":"2025年第三季度的"}]</t>
+  </si>
+  <si>
+    <t>B1006</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析一下千金药业2025收入情况，看看有什么变化。"},{"Q":"绘制近3年的收入趋势图"},{"Q":"绘制水平柱状图"}]</t>
+  </si>
+  <si>
+    <t>B1007</t>
+  </si>
+  <si>
+    <t>[{"Q":"哪些企业是亏钱的？"},{"Q":"“亏钱”在业务场景中，指的是经审计财务报表的核心利润指标为负的数据。"}]</t>
+  </si>
+  <si>
+    <t>B1008</t>
+  </si>
+  <si>
+    <t>[{"Q":"香雪制药2024年研发费用是多少"},{"Q":"销售费用是多少"}]</t>
+  </si>
+  <si>
+    <t>B1009</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，66家中药公司中“营业总收入”和“净利润”均排名前五的公司有哪些？请列出其股票代码、简称、营业总收入（万元）、净利润（万元）"}]</t>
+  </si>
+  <si>
+    <t>B1010</t>
+  </si>
+  <si>
+    <t>[{"Q":"对比白云山（600332）2022年至2025年第三季度的“营业总收入同比增长率”，展示各报告期的增长率数据，并生成趋势折线图。"}]</t>
+  </si>
+  <si>
+    <t>B1011</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，资产负债率（负债总额/资产总额）超过60%的中药公司有哪些？请列出股票代码、简称、资产负债率（%）。"}]</t>
+  </si>
+  <si>
+    <t>B1012</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“经营性现金流量净额”为负数且“净利润”为正数的公司有哪些？请列出其股票代码、简称、经营性现金流净额（万元）、净利润（万元）。"}]</t>
+  </si>
+  <si>
+    <t>B1013</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“销售毛利率”和“销售净利率”均高于行业均值的中药公司有哪些？请同步输出行业均值和公司具体数值。"}]</t>
+  </si>
+  <si>
+    <t>B1014</t>
+  </si>
+  <si>
+    <t>[{"Q":"云南白药（000538）2025年第三季度的“营业总收入环比增长率”与2024年第三季度的环比增长率相比，变化了多少？请展示两年同期的环比数据。"}]</t>
+  </si>
+  <si>
+    <t>B1015</t>
+  </si>
+  <si>
+    <t>[{"Q":"2022-2025年第三季度，“加权平均净资产收益率（扣非）”连续四个报告期均超过10%的公司有哪些？请列出股票代码、简称及各期收益率。"}]</t>
+  </si>
+  <si>
+    <t>B1016</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“资产-存货”金额排名前三的公司，其“营业总收入”与存货金额的比值分别是多少？请列出公司简称、存货（万元）、营业总收入（万元）及比值。"}]</t>
+  </si>
+  <si>
+    <t>B1017</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“资产-应收账款”占“营业总收入”比例超过30%的公司有哪些？请列出股票代码、简称、应收账款占比（%）。"}]</t>
+  </si>
+  <si>
+    <t>B1018</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“净利润同比增长率”波动最大（即与2024年同期相比，增幅或降幅绝对值最大）的3家公司是哪些？请展示具体增长率。"}]</t>
+  </si>
+  <si>
+    <t>B1019</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“营业总支出-研发费用”占“营业总收入”比例排名前五的公司有哪些？请列出简称、研发费用占比（%）。"}]</t>
+  </si>
+  <si>
+    <t>B1020</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“股东权益-未分配利润”金额排名前五的公司，其2025年的“净利润”占未分配利润的比例是多少？请展示具体数值。"}]</t>
+  </si>
+  <si>
+    <t>B1021</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“负债-短期借款”金额超过“资产-货币资金”金额的公司有哪些？请列出简称、短期借款（万元）、货币资金（万元）。"}]</t>
+  </si>
+  <si>
+    <t>B1022</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“核心业绩指标表”中的“营业总收入”与“利润表”中的“营业总收入”不一致的公司有哪些？请列出股票代码及两个表中的数值。"}]</t>
+  </si>
+  <si>
+    <t>B1023</t>
+  </si>
+  <si>
+    <t>[{"Q":"计算2022年财报至2025年第三季度，66家公司的营业总收入复合增长率，排名前三的公司是哪些？请展示复合增长率（%）。"}]</t>
+  </si>
+  <si>
+    <t>B1024</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“扣非净利润”与“净利润”的差值绝对值最大的5家公司是哪些？请列出简称、净利润（万元）、扣非净利润（万元）及差值。"}]</t>
+  </si>
+  <si>
+    <t>B1025</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“投资性现金流量净额”为正数（即投资现金流入大于流出）的公司有多少家？请列出其中营收排名前三的公司简称及投资现金流净额（万元）。"}]</t>
+  </si>
+  <si>
+    <t>B1026</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“营业总支出-销售费用”占“营业总收入”比例低于行业均值的公司中，“净利润”最高的3家是哪些？请同步展示行业均值。"}]</t>
+  </si>
+  <si>
+    <t>B1027</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度，“资产-总资产同比增长率”超过“营业总收入同比增长率”10个百分点以上的公司有哪些？请列出简称、资产增长率（%）、营收增长率（%）。"}]</t>
+  </si>
+  <si>
+    <t>B1028</t>
+  </si>
+  <si>
+    <t>[{"Q":"对比白云山（600332）、云南白药（000538）、片仔癀（600436）2022-2025年第三季度的“净利润（万元）”，生成多系列折线图展示趋势。"}]</t>
+  </si>
+  <si>
+    <t>B1029</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度所有上市公司的股票代码、公司简称和营业总收入（单位：万元），按营业总收入从高到低排序。"}]</t>
+  </si>
+  <si>
+    <t>B1030</t>
+  </si>
+  <si>
+    <t>[{"Q":"从资产负债表中提取片仔癀（600436）2022年全年的资产总额、负债总额、股东权益总额（单位：万元）"}]</t>
+  </si>
+  <si>
+    <t>B1031</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度净利润为负数的中药公司数量，并列出这些公司的股票代码和简称。"}]</t>
+  </si>
+  <si>
+    <t>B1032</t>
+  </si>
+  <si>
+    <t>[{"Q":"关联核心业绩指标表和利润表，查询2025年第三季度每家公司的股票代码、简称、营业总收入（取自核心业绩指标表）、销售毛利率（利润表中（营业收入-营业成本）/营业收入*100），保留两位小数。"}]</t>
+  </si>
+  <si>
+    <t>B1033</t>
+  </si>
+  <si>
+    <t>[{"Q":"结合现金流量表和利润表，查询2024年全年所有公司的股票代码、简称、净利润（利润表）、经营性现金流量净额（现金流量表），筛选出经营性现金流量净额大于净利润的公司。"}]</t>
+  </si>
+  <si>
+    <t>B1034</t>
+  </si>
+  <si>
+    <t>[{"Q":"计算云南白药（000538）2025年第三季度营业总收入的环比增长率（环比增长率=(本季度值-上季度值)/上季度值*100），并展示2025年第二季度和第三季度的营业总收入（万元）及环比增长率（保留两位小数）。"}]</t>
+  </si>
+  <si>
+    <t>B1035</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度各公司净利润同比增长率（同比增长率=(2025Q3值-2024Q3值)/2024Q3值*100），找出同比增长率超过50%的公司，列出股票代码、简称和同比增长率"}]</t>
+  </si>
+  <si>
+    <t>B1036</t>
+  </si>
+  <si>
+    <t>[{"Q":"计算2025年第三季度66家中药公司的资产负债率（负债总额/资产总额*100）行业均值，同时列出资产负债率最高的前10家公司的股票代码、简称和资产负债率（保留两位小数）。"}]</t>
+  </si>
+  <si>
+    <t>B1037</t>
+  </si>
+  <si>
+    <t>[{"Q":"按2025年第三季度的销售净利率（净利润/营业总收入*100）分组，统计销售净利率在0-5%、5%-10%、10%以上三个区间的公司数量。"}]</t>
+  </si>
+  <si>
+    <t>B1038</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度满足以下条件的公司：营业总收入超过10亿元（即100000万元）、资产负债率低于40%、经营性现金流量净额为正，列出股票代码、简称、营业总收入、资产负债率、经营性现金流量净额。"}]</t>
+  </si>
+  <si>
+    <t>B1039</t>
+  </si>
+  <si>
+    <t>[{"Q":"找出2022-2025年第三季度期间，连续四个报告期扣非净利润均超过1亿元的公司，列出股票代码、简称及各报告期的扣非净利润（万元）"}]</t>
+  </si>
+  <si>
+    <t>B1040</t>
+  </si>
+  <si>
+    <t>[{"Q":"关联资产负债表和现金流量表，查询2025年第三季度货币资金占总资产比例超过20%，且投资性现金流量净额为负数的公司，按货币资金占比从高到低排序。"}]</t>
+  </si>
+  <si>
+    <t>B1041</t>
+  </si>
+  <si>
+    <t>[{"Q":"检查2025年第三季度核心业绩指标表中的“营业总收入”与利润表中的“营业收入”数值不一致的公司，列出股票代码、两个表中的数值及差值（绝对值）。"}]</t>
+  </si>
+  <si>
+    <t>B1042</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度研发费用占营业总收入比例最高的5家公司，要求同时展示研发费用（万元）、营业总收入（万元）、研发费用占比（保留两位小数）"}]</t>
+  </si>
+  <si>
+    <t>B1043</t>
+  </si>
+  <si>
+    <t>[{"Q":"计算2025年第三季度66家公司的净利润中位数，找出净利润高于中位数且销售毛利率低于行业均值的公司，列出股票代码、简称、净利润、销售毛利率。"}]</t>
+  </si>
+  <si>
+    <t>B1044</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度营业总收入排名前五的中药公司有哪些？"},{"Q":"这五家公司的净利润分别是多少"},{"Q":"它们的净利润同比增长率和行业均值相比如何"}]</t>
+  </si>
+  <si>
+    <t>B1045</t>
+  </si>
+  <si>
+    <t>[{"Q":"云南白药2022-2025年第三季度的资产负债率变化趋势"},{"Q":"这个趋势和白云山的同期变化趋势对比，差异在哪里"},{"Q":"导致两者差异的核心财务指标（如负债总额、资产总额）变化是什么"}]</t>
+  </si>
+  <si>
+    <t>B1046</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度经营性现金流量净额为负的公司有多少家"},{"Q":"这些公司中，资产负债率超过60%的有几家"}]</t>
+  </si>
+  <si>
+    <t>B1047</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年第三季度研发费用占比前十的中药公司"},{"Q":"这些公司的销售毛利率在利润表中表现如何"}]</t>
+  </si>
+  <si>
+    <t>B1048</t>
+  </si>
+  <si>
+    <t>[{"Q":"2024年第三季度净利润排名前三的公司？"},{"Q":"这些公司2025年第三季度的净利润排名有没有变化？"},{"Q":"排名变化最大的公司，其营业总收入的变化幅度是多少？"}]</t>
+  </si>
+  <si>
+    <t>B1049</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度66家中药公司营业总收入排名前十的公司，用条形图展示排名"}]</t>
+  </si>
+  <si>
+    <t>B1050</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析云南白药2022-2025年第三季度净利润的变化趋势，用折线图展示"}]</t>
+  </si>
+  <si>
+    <t>B1051</t>
+  </si>
+  <si>
+    <t>[{"Q":"对比白云山、云南白药、片仔癀2025年第三季度的核心盈利能力指标（销售毛利率、销售净利率、ROE），用雷达图展示差异"}]</t>
+  </si>
+  <si>
+    <t>B1052</t>
+  </si>
+  <si>
+    <t>[{"Q":"统计2025年第三季度中药公司资产负债率的分布情况（按0-30%、30%-50%、50%-70%、70%以上分组），用饼图展示各组公司数量占比"}]</t>
+  </si>
+  <si>
+    <t>B1053</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度经营性现金流量净额与净利润的比值分布，用直方图展示"}]</t>
+  </si>
+  <si>
+    <t>B1054</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析2022-2025年第三季度中药行业平均研发费用占比的变化趋势，用折线图展示"}]</t>
+  </si>
+  <si>
+    <t>B1055</t>
+  </si>
+  <si>
+    <t>[{"Q":"对比2024年和2025年第三季度净利润同比增长率前十公司的名单变化，用双条形图展示两年排名及增长率"}]</t>
+  </si>
+  <si>
+    <t>B1056</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度存货周转率最高的五家公司，用条形图展示其周转率数值"}]</t>
+  </si>
+  <si>
+    <t>B1057</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析2025年第三季度营业总收入与净利润的相关性，用散点图展示"}]</t>
+  </si>
+  <si>
+    <t>B1058</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度短期借款超过货币资金的公司，用表格列出具体数据，并用柱状图对比这两项指标的差额"}]</t>
+  </si>
+  <si>
+    <t>B1059</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析片仔癀2022-2025年第三季度扣非净利润占净利润的比例变化，用折线图展示"}]</t>
+  </si>
+  <si>
+    <t>B1060</t>
+  </si>
+  <si>
+    <t>[{"Q":"对比2025年第三季度研发费用占比前十与后十公司的净利润同比增长率，用箱线图展示两组数据的分布差异"}]</t>
+  </si>
+  <si>
+    <t>B1061</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度投资性现金流量净额的正负分布情况，用柱状图展示正负公司的数量及净额均值"}]</t>
+  </si>
+  <si>
+    <t>B1062</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析2025年第三季度营业成本占营业总收入的比例排名后十的公司，用条形图展示占比数值"}]</t>
+  </si>
+  <si>
+    <t>B1063</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析2022-2025年第三季度66家中药公司营业总收入的复合增长率分布，用直方图展示"}]</t>
+  </si>
+  <si>
+    <t>B1064</t>
+  </si>
+  <si>
+    <t>[{"Q":"对比2025年第三季度销售费用率低于行业均值和高于行业均值公司的平均净利润率，用柱状图展示差异"}]</t>
+  </si>
+  <si>
+    <t>B1065</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询2025年第三季度出口业务占比超过10%的中药公司，用表格列出其出口占比、营业总收入增长率，并用折线图展示它们的营收增长趋势"}]</t>
+  </si>
+  <si>
+    <t>B1066</t>
+  </si>
+  <si>
+    <t>[{"Q":"哪些公司的业绩比较好？"},{"Q":"2025年第三季度，2家中药上市公司中，营业总收入和净利润均排名前十的公司"}]</t>
+  </si>
+  <si>
+    <t>B1067</t>
+  </si>
+  <si>
+    <t>[{"Q":"中药公司的资产负债率情况如何"},{"Q":"2025年第三季度，66家中药上市公司的资产负债率均值是多少"}]</t>
+  </si>
+  <si>
+    <t>B1068</t>
+  </si>
+  <si>
+    <t>[{"Q":"分析中药行业的盈利能力"},{"Q":"2025年第三季度，66家中药上市公司的平均销售毛利率、销售净利率分别是多少？请结合数值分析行业整体盈利能力"}]</t>
+  </si>
+  <si>
+    <t>B1069</t>
+  </si>
+  <si>
+    <t>[{"Q":"2025年的财务数据怎么样？"},{"Q":"2025年第三季度，66家中药上市公司的营业总收入、净利润均值分别是多少？与2024年同期相比增长率如何？"}]</t>
+  </si>
+  <si>
+    <t>B1070</t>
+  </si>
+  <si>
+    <t>[{"Q":"查询净利润同比增长的公司"},{"Q":"2025年第三季度，66家中药上市公司中，净利润同比增长率超过20%的公司有哪些？列出股票代码、简称及具体增长率"}]</t>
   </si>
 </sst>
 </file>
@@ -78,7 +486,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -678,15 +1086,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1002,9 +1413,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="2"/>
   <cols>
+    <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="17.7657657657658" customWidth="1"/>
     <col min="3" max="3" width="101" customWidth="1"/>
   </cols>
@@ -1013,33 +1425,781 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
